--- a/output/2026-09-17_深紅動能見底訊號_參數設定.xlsx
+++ b/output/2026-09-17_深紅動能見底訊號_參數設定.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_真正的參數" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_建議設定" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_怎麼跑" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TV_連結" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +25,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,6 +56,16 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -155,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -178,6 +189,15 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -749,6 +769,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -763,6 +784,7 @@
       <c r="G3" s="3" t="n"/>
       <c r="H3" s="4" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
@@ -784,6 +806,7 @@
       <c r="G6" s="3" t="n"/>
       <c r="H6" s="4" t="n"/>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -953,6 +976,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
@@ -1161,6 +1185,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
@@ -1174,6 +1199,7 @@
       <c r="F9" s="3" t="n"/>
       <c r="G9" s="4" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
@@ -1366,6 +1392,7 @@
       </c>
       <c r="C9" s="7" t="inlineStr"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
@@ -1705,6 +1732,7 @@
       <c r="H2" s="3" t="n"/>
       <c r="I2" s="4" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -2464,6 +2492,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2608,6 +2637,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
@@ -2678,4 +2708,64 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>TradingView 連結索引（本檔案出現過的所有代號）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>原地已加連結的儲存格：0 個。另有 0 個儲存格同時提及多個代號 —— Excel 不支援在單一儲存格內為部分文字加連結，故該類儲存格不在原地處理，改由本表覆蓋。點擊下方連結即可開啟該代號的 TradingView 圖表。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>代號</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>出現位置</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>